--- a/site/ADP-Workforce-Now-Microsoft-365-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Microsoft-365-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,72 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Microsoft-365-Integration-Guide/#h_01M0YW88TBXGZ4AGZ1XNNYQX8N</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Prerequisites</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>h_01M0YWHK9NV730T3B37Q7Q8TCY</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Microsoft-365-Integration-Guide/#h_01M0YWHK9NV730T3B37Q7Q8TCY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Integration Setup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Microsoft-365-Integration-Guide/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Create Integration</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>h_01KFN5VN33W6V4TKMMX55CFV6R</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Microsoft-365-Integration-Guide/#h_01KFN5VN33W6V4TKMMX55CFV6R</t>
         </is>
       </c>
     </row>

--- a/site/ADP-Workforce-Now-Microsoft-365-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Microsoft-365-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,6 +548,138 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>h_01M0YX23YM96WBXYRJDEK01C6S</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Microsoft-365-Integration-Guide/#h_01M0YX23YM96WBXYRJDEK01C6S</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Applications</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01M0Z4X00EDNR0JKXQ7ANGYCHT</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Microsoft-365-Integration-Guide/#h_01M0Z4X00EDNR0JKXQ7ANGYCHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01M0Z3Y9ZMZB3NK7ETS88YP3WP</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Microsoft-365-Integration-Guide/#h_01M0Z3Y9ZMZB3NK7ETS88YP3WP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01M0Z4QH25P7PJ44G5PB7XPETE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Microsoft-365-Integration-Guide/#h_01M0Z4QH25P7PJ44G5PB7XPETE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Microsoft-365-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Microsoft-365-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/ADP-Workforce-Now-Microsoft-365-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Microsoft-365-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,54 +627,76 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01M0Z4QH25P7PJ44G5PB7XPETE</t>
+          <t>h_01M10WFCXRQHSM3FP33Y593C9F</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Microsoft-365-Integration-Guide/#h_01M0Z4QH25P7PJ44G5PB7XPETE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Microsoft-365-Integration-Guide/#h_01M10WFCXRQHSM3FP33Y593C9F</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01M0Z4QH25P7PJ44G5PB7XPETE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Microsoft-365-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Microsoft-365-Integration-Guide/#h_01M0Z4QH25P7PJ44G5PB7XPETE</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Microsoft-365-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Microsoft-365-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
